--- a/content/xls/NSO_p_regions_01.01.2025.xlsx
+++ b/content/xls/NSO_p_regions_01.01.2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FE7A30CC-D3F1-48BA-848C-A16140858DF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33D802F-8CD9-4ACF-ADF8-7C56CAF323D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
@@ -151,7 +151,7 @@
   </si>
   <si>
     <r>
-      <t>Изменение уровня развития дистанционного банковского обслуживани</t>
+      <t>Изменение уровня потребности в развитии дистанционного банковского обслуживани</t>
     </r>
     <r>
       <rPr>
@@ -634,7 +634,7 @@
     <col min="12" max="12" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="103.4" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="118.15" x14ac:dyDescent="0.3">
       <c r="A1" s="9" t="s">
         <v>33</v>
       </c>

--- a/content/xls/NSO_p_regions_01.01.2025.xlsx
+++ b/content/xls/NSO_p_regions_01.01.2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B33D802F-8CD9-4ACF-ADF8-7C56CAF323D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5187CD3D-9160-4E1C-8226-D0888EC9469B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
@@ -133,9 +133,6 @@
   </si>
   <si>
     <t>Количество точек финансового доступа, ед.</t>
-  </si>
-  <si>
-    <t>Количество Финансовых помощников, ед.</t>
   </si>
   <si>
     <t>Количество торговых точек с сервисом "Выдача наличных на кассе", ед.</t>
@@ -187,6 +184,9 @@
       </rPr>
       <t>, п.п.</t>
     </r>
+  </si>
+  <si>
+    <t>Количество финансовых помощников, ед.</t>
   </si>
 </sst>
 </file>
@@ -645,7 +645,7 @@
         <v>34</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E1" s="9" t="s">
         <v>31</v>
@@ -657,19 +657,19 @@
         <v>35</v>
       </c>
       <c r="H1" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I1" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="J1" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="J1" s="9" t="s">
+      <c r="K1" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="K1" s="9" t="s">
+      <c r="L1" s="9" t="s">
         <v>39</v>
-      </c>
-      <c r="L1" s="9" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">

--- a/content/xls/NSO_p_regions_01.01.2025.xlsx
+++ b/content/xls/NSO_p_regions_01.01.2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Python\InfPanel\content\xls\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5187CD3D-9160-4E1C-8226-D0888EC9469B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06E40F8B-6C08-4009-98D8-F9D271DE4F36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-111" yWindow="-111" windowWidth="31729" windowHeight="17342" xr2:uid="{F8C46831-A766-4421-B6E6-28A897387E31}"/>
   </bookViews>
